--- a/artfynd/A 50909-2022 artfynd.xlsx
+++ b/artfynd/A 50909-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50909-2022 artfynd.xlsx
+++ b/artfynd/A 50909-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY101"/>
+  <dimension ref="A1:AZ101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045893</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045896</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544391</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544402</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544413</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111959818</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111959819</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1487,6 +1527,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112036909</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1588,6 +1633,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037006</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1689,6 +1739,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037088</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1790,6 +1845,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037108</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1891,6 +1951,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037492</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045882</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2105,6 +2175,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045885</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2212,6 +2287,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045891</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2309,6 +2389,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111959820</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2406,6 +2491,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111959821</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2503,6 +2593,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111959822</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2600,6 +2695,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111959823</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2701,6 +2801,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112036981</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2802,6 +2907,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037501</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2903,6 +3013,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037792</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3004,6 +3119,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037831</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3111,6 +3231,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045877</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3218,6 +3343,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045889</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3320,6 +3450,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544387</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3422,6 +3557,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544390</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3519,6 +3659,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111959810</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3616,6 +3761,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111959811</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3717,6 +3867,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037000</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3818,6 +3973,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037496</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3919,6 +4079,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037825</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4026,6 +4191,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045878</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4133,6 +4303,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045894</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4235,6 +4410,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544394</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4337,6 +4517,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544411</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4434,6 +4619,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111959824</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4535,6 +4725,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112036938</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4642,6 +4837,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045881</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4749,6 +4949,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045901</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4850,6 +5055,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037150</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4951,6 +5161,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037653</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5058,6 +5273,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045880</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5165,6 +5385,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045887</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5262,6 +5487,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111959832</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5359,6 +5589,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111959833</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5456,6 +5691,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111959834</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5558,6 +5798,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544393</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5660,6 +5905,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544415</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5757,6 +6007,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111959825</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5854,6 +6109,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111959826</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5955,6 +6215,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037364</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6056,6 +6321,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037760</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6163,6 +6433,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045883</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6265,6 +6540,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544388</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6367,6 +6647,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544400</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6469,6 +6754,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544410</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6571,6 +6861,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544414</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6668,6 +6963,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111959829</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6765,6 +7065,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111959830</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6862,6 +7167,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111959831</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6972,6 +7282,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112036871</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7073,6 +7388,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037094</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7174,6 +7494,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037172</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7280,6 +7605,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037509</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7381,6 +7711,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037585</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7487,6 +7822,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037714</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7588,6 +7928,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037788</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7689,6 +8034,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037877</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7796,6 +8146,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045876</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7903,6 +8258,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045895</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8010,6 +8370,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045900</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8112,6 +8477,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544401</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8209,6 +8579,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111959809</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8316,6 +8691,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045892</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8423,6 +8803,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045897</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8530,6 +8915,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045902</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8632,6 +9022,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544395</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8734,6 +9129,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544408</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8836,6 +9236,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544412</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8938,6 +9343,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544389</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9040,6 +9450,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544392</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9142,6 +9557,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544409</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9247,6 +9667,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111959815</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9352,6 +9777,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111985424</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9457,6 +9887,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111985425</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9562,6 +9997,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111985426</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9667,6 +10107,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111985428</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9772,6 +10217,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111985429</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9882,6 +10332,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112036972</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9992,6 +10447,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037072</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10102,6 +10562,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037188</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10212,6 +10677,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037401</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10322,6 +10792,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037867</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10432,6 +10907,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037927</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10544,6 +11024,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045884</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10656,6 +11141,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045886</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10768,6 +11258,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045898</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10880,6 +11375,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045899</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10992,8 +11492,115 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045903</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>